--- a/ContractFC.xlsx
+++ b/ContractFC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\DASHBOARD สัญญา\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F886E783-B647-456A-83DD-5578F68F63C0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAFFCA6E-2CC3-4114-A073-0DB02713A8D6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{BF4525B0-8BC8-4599-A816-84CCD5BC5322}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$F$292</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$F$293</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -690,7 +690,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D279" authorId="0" shapeId="0" xr:uid="{F4A6A91D-EC2F-438C-8DD1-DC03541BA94A}">
+    <comment ref="D280" authorId="0" shapeId="0" xr:uid="{F4A6A91D-EC2F-438C-8DD1-DC03541BA94A}">
       <text>
         <r>
           <rPr>
@@ -719,7 +719,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1449" uniqueCount="844">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1453" uniqueCount="845">
   <si>
     <t>กิจการ</t>
   </si>
@@ -2618,9 +2618,6 @@
     <t>FC ปากชม</t>
   </si>
   <si>
-    <t>1 ก.ค. 66</t>
-  </si>
-  <si>
     <t>บจก.นาซ่า ซีแพค ภูกระดึง</t>
   </si>
   <si>
@@ -3420,6 +3417,12 @@
   </si>
   <si>
     <t>FC407</t>
+  </si>
+  <si>
+    <t>FC414</t>
+  </si>
+  <si>
+    <t>ทับปุด 2</t>
   </si>
 </sst>
 </file>
@@ -4011,7 +4014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5749CB8-12FD-40F3-B232-B322BA62DBAA}">
-  <dimension ref="A1:F292"/>
+  <dimension ref="A1:F293"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="9.90625" bestFit="1" customWidth="1"/>
@@ -4340,7 +4343,7 @@
         <v>50</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>54</v>
@@ -4600,7 +4603,7 @@
         <v>8</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>89</v>
@@ -4820,7 +4823,7 @@
         <v>111</v>
       </c>
       <c r="C41" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>120</v>
@@ -5200,7 +5203,7 @@
         <v>172</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>173</v>
@@ -5220,7 +5223,7 @@
         <v>172</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>175</v>
@@ -5700,7 +5703,7 @@
         <v>249</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>252</v>
@@ -6500,7 +6503,7 @@
         <v>361</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="D125" s="3" t="s">
         <v>364</v>
@@ -8205,11 +8208,9 @@
       <c r="D210" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="E210" s="17" t="s">
-        <v>596</v>
-      </c>
+      <c r="E210" s="17"/>
       <c r="F210" s="4">
-        <v>244530</v>
+        <v>245626</v>
       </c>
     </row>
     <row r="211" spans="1:6" ht="15" thickBot="1">
@@ -8217,13 +8218,13 @@
         <v>402</v>
       </c>
       <c r="B211" s="5" t="s">
+        <v>596</v>
+      </c>
+      <c r="C211" s="3" t="s">
         <v>597</v>
       </c>
-      <c r="C211" s="3" t="s">
+      <c r="D211" s="3" t="s">
         <v>598</v>
-      </c>
-      <c r="D211" s="3" t="s">
-        <v>599</v>
       </c>
       <c r="E211" s="16" t="s">
         <v>406</v>
@@ -8240,10 +8241,10 @@
         <v>590</v>
       </c>
       <c r="C212" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="D212" s="3" t="s">
         <v>600</v>
-      </c>
-      <c r="D212" s="3" t="s">
-        <v>601</v>
       </c>
       <c r="E212" s="16" t="s">
         <v>412</v>
@@ -8257,19 +8258,19 @@
         <v>402</v>
       </c>
       <c r="B213" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="C213" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="C213" s="3" t="s">
+      <c r="D213" s="3" t="s">
         <v>603</v>
       </c>
-      <c r="D213" s="3" t="s">
+      <c r="E213" s="16" t="s">
         <v>604</v>
       </c>
-      <c r="E213" s="16" t="s">
-        <v>605</v>
-      </c>
       <c r="F213" s="4">
-        <v>244530</v>
+        <v>245626</v>
       </c>
     </row>
     <row r="214" spans="1:6" ht="15" thickBot="1">
@@ -8280,10 +8281,10 @@
         <v>485</v>
       </c>
       <c r="C214" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="D214" s="3" t="s">
         <v>606</v>
-      </c>
-      <c r="D214" s="3" t="s">
-        <v>607</v>
       </c>
       <c r="E214" s="16" t="s">
         <v>412</v>
@@ -8300,10 +8301,10 @@
         <v>485</v>
       </c>
       <c r="C215" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="D215" s="3" t="s">
         <v>608</v>
-      </c>
-      <c r="D215" s="3" t="s">
-        <v>609</v>
       </c>
       <c r="E215" s="16" t="s">
         <v>429</v>
@@ -8320,10 +8321,10 @@
         <v>485</v>
       </c>
       <c r="C216" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="D216" s="3" t="s">
         <v>610</v>
-      </c>
-      <c r="D216" s="3" t="s">
-        <v>611</v>
       </c>
       <c r="E216" s="16" t="s">
         <v>470</v>
@@ -8337,13 +8338,13 @@
         <v>402</v>
       </c>
       <c r="B217" s="5" t="s">
+        <v>611</v>
+      </c>
+      <c r="C217" s="3" t="s">
         <v>612</v>
       </c>
-      <c r="C217" s="3" t="s">
+      <c r="D217" s="3" t="s">
         <v>613</v>
-      </c>
-      <c r="D217" s="3" t="s">
-        <v>614</v>
       </c>
       <c r="E217" s="16" t="s">
         <v>470</v>
@@ -8357,16 +8358,16 @@
         <v>402</v>
       </c>
       <c r="B218" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>842</v>
+      </c>
+      <c r="D218" s="3" t="s">
         <v>615</v>
       </c>
-      <c r="C218" s="3" t="s">
-        <v>843</v>
-      </c>
-      <c r="D218" s="3" t="s">
+      <c r="E218" s="16" t="s">
         <v>616</v>
-      </c>
-      <c r="E218" s="16" t="s">
-        <v>617</v>
       </c>
       <c r="F218" s="4">
         <v>245260</v>
@@ -8377,13 +8378,13 @@
         <v>402</v>
       </c>
       <c r="B219" s="5" t="s">
+        <v>617</v>
+      </c>
+      <c r="C219" s="3" t="s">
         <v>618</v>
       </c>
-      <c r="C219" s="3" t="s">
+      <c r="D219" s="3" t="s">
         <v>619</v>
-      </c>
-      <c r="D219" s="3" t="s">
-        <v>620</v>
       </c>
       <c r="E219" s="16" t="s">
         <v>406</v>
@@ -8397,16 +8398,16 @@
         <v>402</v>
       </c>
       <c r="B220" s="5" t="s">
+        <v>620</v>
+      </c>
+      <c r="C220" s="3" t="s">
         <v>621</v>
       </c>
-      <c r="C220" s="3" t="s">
+      <c r="D220" s="3" t="s">
         <v>622</v>
       </c>
-      <c r="D220" s="3" t="s">
+      <c r="E220" s="16" t="s">
         <v>623</v>
-      </c>
-      <c r="E220" s="16" t="s">
-        <v>624</v>
       </c>
       <c r="F220" s="4">
         <v>245626</v>
@@ -8417,16 +8418,16 @@
         <v>402</v>
       </c>
       <c r="B221" s="5" t="s">
+        <v>624</v>
+      </c>
+      <c r="C221" s="24" t="s">
         <v>625</v>
       </c>
-      <c r="C221" s="24" t="s">
+      <c r="D221" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="D221" s="3" t="s">
+      <c r="E221" s="16" t="s">
         <v>627</v>
-      </c>
-      <c r="E221" s="16" t="s">
-        <v>628</v>
       </c>
       <c r="F221" s="4">
         <v>242704</v>
@@ -8437,16 +8438,16 @@
         <v>402</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C222" s="24" t="s">
+        <v>628</v>
+      </c>
+      <c r="D222" s="3" t="s">
         <v>629</v>
       </c>
-      <c r="D222" s="3" t="s">
+      <c r="E222" s="16" t="s">
         <v>630</v>
-      </c>
-      <c r="E222" s="16" t="s">
-        <v>631</v>
       </c>
       <c r="F222" s="4">
         <v>244895</v>
@@ -8457,13 +8458,13 @@
         <v>402</v>
       </c>
       <c r="B223" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="C223" s="3" t="s">
         <v>632</v>
       </c>
-      <c r="C223" s="3" t="s">
+      <c r="D223" s="3" t="s">
         <v>633</v>
-      </c>
-      <c r="D223" s="3" t="s">
-        <v>634</v>
       </c>
       <c r="E223" s="16" t="s">
         <v>429</v>
@@ -8477,13 +8478,13 @@
         <v>402</v>
       </c>
       <c r="B224" s="5" t="s">
+        <v>634</v>
+      </c>
+      <c r="C224" s="3" t="s">
         <v>635</v>
       </c>
-      <c r="C224" s="3" t="s">
+      <c r="D224" s="3" t="s">
         <v>636</v>
-      </c>
-      <c r="D224" s="3" t="s">
-        <v>637</v>
       </c>
       <c r="E224" s="16" t="s">
         <v>406</v>
@@ -8500,13 +8501,13 @@
         <v>488</v>
       </c>
       <c r="C225" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="D225" s="10" t="s">
         <v>638</v>
       </c>
-      <c r="D225" s="10" t="s">
+      <c r="E225" s="16" t="s">
         <v>639</v>
-      </c>
-      <c r="E225" s="16" t="s">
-        <v>640</v>
       </c>
       <c r="F225" s="21">
         <v>243434</v>
@@ -8520,10 +8521,10 @@
         <v>590</v>
       </c>
       <c r="C226" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="D226" s="6" t="s">
         <v>641</v>
-      </c>
-      <c r="D226" s="6" t="s">
-        <v>642</v>
       </c>
       <c r="E226" s="16" t="s">
         <v>429</v>
@@ -8537,16 +8538,16 @@
         <v>402</v>
       </c>
       <c r="B227" s="5" t="s">
+        <v>642</v>
+      </c>
+      <c r="C227" s="6" t="s">
         <v>643</v>
       </c>
-      <c r="C227" s="6" t="s">
+      <c r="D227" s="6" t="s">
         <v>644</v>
       </c>
-      <c r="D227" s="6" t="s">
+      <c r="E227" s="26" t="s">
         <v>645</v>
-      </c>
-      <c r="E227" s="26" t="s">
-        <v>646</v>
       </c>
       <c r="F227" s="27">
         <v>244165</v>
@@ -8557,13 +8558,13 @@
         <v>402</v>
       </c>
       <c r="B228" s="5" t="s">
+        <v>646</v>
+      </c>
+      <c r="C228" s="6" t="s">
         <v>647</v>
       </c>
-      <c r="C228" s="6" t="s">
+      <c r="D228" s="6" t="s">
         <v>648</v>
-      </c>
-      <c r="D228" s="6" t="s">
-        <v>649</v>
       </c>
       <c r="E228" s="17" t="s">
         <v>470</v>
@@ -8577,13 +8578,13 @@
         <v>402</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C229" s="6" t="s">
+        <v>649</v>
+      </c>
+      <c r="D229" s="6" t="s">
         <v>650</v>
-      </c>
-      <c r="D229" s="6" t="s">
-        <v>651</v>
       </c>
       <c r="E229" s="16" t="s">
         <v>429</v>
@@ -8597,13 +8598,13 @@
         <v>402</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C230" s="6" t="s">
+        <v>651</v>
+      </c>
+      <c r="D230" s="28" t="s">
         <v>652</v>
-      </c>
-      <c r="D230" s="28" t="s">
-        <v>653</v>
       </c>
       <c r="E230" s="16" t="s">
         <v>429</v>
@@ -8617,16 +8618,16 @@
         <v>402</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C231" s="6" t="s">
+        <v>653</v>
+      </c>
+      <c r="D231" s="28" t="s">
         <v>654</v>
       </c>
-      <c r="D231" s="28" t="s">
+      <c r="E231" s="17" t="s">
         <v>655</v>
-      </c>
-      <c r="E231" s="17" t="s">
-        <v>656</v>
       </c>
       <c r="F231" s="4">
         <v>245260</v>
@@ -8637,13 +8638,13 @@
         <v>402</v>
       </c>
       <c r="B232" s="5" t="s">
+        <v>656</v>
+      </c>
+      <c r="C232" s="6" t="s">
         <v>657</v>
       </c>
-      <c r="C232" s="6" t="s">
+      <c r="D232" s="6" t="s">
         <v>658</v>
-      </c>
-      <c r="D232" s="6" t="s">
-        <v>659</v>
       </c>
       <c r="E232" s="17" t="s">
         <v>470</v>
@@ -8657,13 +8658,13 @@
         <v>402</v>
       </c>
       <c r="B233" s="5" t="s">
+        <v>659</v>
+      </c>
+      <c r="C233" s="6" t="s">
         <v>660</v>
       </c>
-      <c r="C233" s="6" t="s">
+      <c r="D233" s="6" t="s">
         <v>661</v>
-      </c>
-      <c r="D233" s="6" t="s">
-        <v>662</v>
       </c>
       <c r="E233" s="16" t="s">
         <v>470</v>
@@ -8677,13 +8678,13 @@
         <v>402</v>
       </c>
       <c r="B234" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="C234" s="3" t="s">
         <v>663</v>
       </c>
-      <c r="C234" s="3" t="s">
+      <c r="D234" s="10" t="s">
         <v>664</v>
-      </c>
-      <c r="D234" s="10" t="s">
-        <v>665</v>
       </c>
       <c r="E234" s="16" t="s">
         <v>470</v>
@@ -8697,13 +8698,13 @@
         <v>402</v>
       </c>
       <c r="B235" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="C235" s="3" t="s">
         <v>666</v>
       </c>
-      <c r="C235" s="3" t="s">
+      <c r="D235" s="3" t="s">
         <v>667</v>
-      </c>
-      <c r="D235" s="3" t="s">
-        <v>668</v>
       </c>
       <c r="E235" s="16" t="s">
         <v>520</v>
@@ -8717,13 +8718,13 @@
         <v>402</v>
       </c>
       <c r="B236" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="C236" s="3" t="s">
         <v>669</v>
       </c>
-      <c r="C236" s="3" t="s">
+      <c r="D236" s="3" t="s">
         <v>670</v>
-      </c>
-      <c r="D236" s="3" t="s">
-        <v>671</v>
       </c>
       <c r="E236" s="16" t="s">
         <v>520</v>
@@ -8737,13 +8738,13 @@
         <v>402</v>
       </c>
       <c r="B237" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="C237" s="3" t="s">
         <v>672</v>
       </c>
-      <c r="C237" s="3" t="s">
+      <c r="D237" s="3" t="s">
         <v>673</v>
-      </c>
-      <c r="D237" s="3" t="s">
-        <v>674</v>
       </c>
       <c r="E237" s="16" t="s">
         <v>412</v>
@@ -8757,13 +8758,13 @@
         <v>402</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C238" s="29" t="s">
+        <v>674</v>
+      </c>
+      <c r="D238" s="30" t="s">
         <v>675</v>
-      </c>
-      <c r="D238" s="30" t="s">
-        <v>676</v>
       </c>
       <c r="E238" s="17" t="s">
         <v>470</v>
@@ -8777,13 +8778,13 @@
         <v>402</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C239" s="29" t="s">
+        <v>676</v>
+      </c>
+      <c r="D239" s="30" t="s">
         <v>677</v>
-      </c>
-      <c r="D239" s="30" t="s">
-        <v>678</v>
       </c>
       <c r="E239" s="17" t="s">
         <v>470</v>
@@ -8797,16 +8798,16 @@
         <v>402</v>
       </c>
       <c r="B240" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="C240" s="29" t="s">
         <v>679</v>
       </c>
-      <c r="C240" s="29" t="s">
+      <c r="D240" s="30" t="s">
         <v>680</v>
       </c>
-      <c r="D240" s="30" t="s">
+      <c r="E240" s="17" t="s">
         <v>681</v>
-      </c>
-      <c r="E240" s="17" t="s">
-        <v>682</v>
       </c>
       <c r="F240" s="4">
         <v>245260</v>
@@ -8817,13 +8818,13 @@
         <v>402</v>
       </c>
       <c r="B241" s="8" t="s">
+        <v>682</v>
+      </c>
+      <c r="C241" s="8" t="s">
         <v>683</v>
       </c>
-      <c r="C241" s="8" t="s">
+      <c r="D241" s="8" t="s">
         <v>684</v>
-      </c>
-      <c r="D241" s="8" t="s">
-        <v>685</v>
       </c>
       <c r="E241" s="17" t="s">
         <v>470</v>
@@ -8837,13 +8838,13 @@
         <v>402</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C242" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="D242" s="8" t="s">
         <v>686</v>
-      </c>
-      <c r="D242" s="8" t="s">
-        <v>687</v>
       </c>
       <c r="E242" s="16" t="s">
         <v>470</v>
@@ -8857,13 +8858,13 @@
         <v>402</v>
       </c>
       <c r="B243" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="C243" s="29" t="s">
         <v>688</v>
       </c>
-      <c r="C243" s="29" t="s">
+      <c r="D243" s="30" t="s">
         <v>689</v>
-      </c>
-      <c r="D243" s="30" t="s">
-        <v>690</v>
       </c>
       <c r="E243" s="17" t="s">
         <v>412</v>
@@ -8877,13 +8878,13 @@
         <v>402</v>
       </c>
       <c r="B244" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="C244" s="3" t="s">
         <v>691</v>
       </c>
-      <c r="C244" s="3" t="s">
+      <c r="D244" s="3" t="s">
         <v>692</v>
-      </c>
-      <c r="D244" s="3" t="s">
-        <v>693</v>
       </c>
       <c r="E244" s="16" t="s">
         <v>520</v>
@@ -8897,13 +8898,13 @@
         <v>402</v>
       </c>
       <c r="B245" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="C245" s="3" t="s">
         <v>694</v>
       </c>
-      <c r="C245" s="3" t="s">
+      <c r="D245" s="3" t="s">
         <v>695</v>
-      </c>
-      <c r="D245" s="3" t="s">
-        <v>696</v>
       </c>
       <c r="E245" s="16" t="s">
         <v>412</v>
@@ -8917,13 +8918,13 @@
         <v>402</v>
       </c>
       <c r="B246" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="C246" s="29" t="s">
         <v>697</v>
       </c>
-      <c r="C246" s="29" t="s">
+      <c r="D246" s="28" t="s">
         <v>698</v>
-      </c>
-      <c r="D246" s="28" t="s">
-        <v>699</v>
       </c>
       <c r="E246" s="17" t="s">
         <v>520</v>
@@ -8937,13 +8938,13 @@
         <v>402</v>
       </c>
       <c r="B247" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="C247" s="29" t="s">
         <v>700</v>
       </c>
-      <c r="C247" s="29" t="s">
+      <c r="D247" s="28" t="s">
         <v>701</v>
-      </c>
-      <c r="D247" s="28" t="s">
-        <v>702</v>
       </c>
       <c r="E247" s="17" t="s">
         <v>520</v>
@@ -8957,16 +8958,16 @@
         <v>402</v>
       </c>
       <c r="B248" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="C248" s="29" t="s">
         <v>703</v>
       </c>
-      <c r="C248" s="29" t="s">
+      <c r="D248" s="28" t="s">
         <v>704</v>
       </c>
-      <c r="D248" s="28" t="s">
+      <c r="E248" s="17" t="s">
         <v>705</v>
-      </c>
-      <c r="E248" s="17" t="s">
-        <v>706</v>
       </c>
       <c r="F248" s="4">
         <v>245260</v>
@@ -8977,13 +8978,13 @@
         <v>402</v>
       </c>
       <c r="B249" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="C249" s="6" t="s">
         <v>707</v>
       </c>
-      <c r="C249" s="6" t="s">
+      <c r="D249" s="6" t="s">
         <v>708</v>
-      </c>
-      <c r="D249" s="6" t="s">
-        <v>709</v>
       </c>
       <c r="E249" s="16" t="s">
         <v>406</v>
@@ -8994,19 +8995,19 @@
     </row>
     <row r="250" spans="1:6" ht="15" thickBot="1">
       <c r="A250" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="B250" s="3" t="s">
         <v>710</v>
       </c>
-      <c r="B250" s="3" t="s">
+      <c r="C250" s="8" t="s">
         <v>711</v>
       </c>
-      <c r="C250" s="8" t="s">
+      <c r="D250" s="10" t="s">
         <v>712</v>
       </c>
-      <c r="D250" s="10" t="s">
+      <c r="E250" s="17" t="s">
         <v>713</v>
-      </c>
-      <c r="E250" s="17" t="s">
-        <v>714</v>
       </c>
       <c r="F250" s="4">
         <v>244987</v>
@@ -9014,19 +9015,19 @@
     </row>
     <row r="251" spans="1:6" ht="15" thickBot="1">
       <c r="A251" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B251" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="C251" s="8" t="s">
         <v>715</v>
       </c>
-      <c r="C251" s="8" t="s">
+      <c r="D251" s="8" t="s">
         <v>716</v>
       </c>
-      <c r="D251" s="8" t="s">
+      <c r="E251" s="17" t="s">
         <v>717</v>
-      </c>
-      <c r="E251" s="17" t="s">
-        <v>718</v>
       </c>
       <c r="F251" s="4">
         <v>244622</v>
@@ -9034,19 +9035,19 @@
     </row>
     <row r="252" spans="1:6" ht="15" thickBot="1">
       <c r="A252" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B252" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="C252" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C252" s="8" t="s">
+      <c r="D252" s="8" t="s">
         <v>720</v>
       </c>
-      <c r="D252" s="8" t="s">
-        <v>721</v>
-      </c>
       <c r="E252" s="17" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F252" s="4">
         <v>244987</v>
@@ -9054,19 +9055,19 @@
     </row>
     <row r="253" spans="1:6" ht="15" thickBot="1">
       <c r="A253" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B253" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="C253" s="8" t="s">
         <v>722</v>
       </c>
-      <c r="C253" s="8" t="s">
+      <c r="D253" s="8" t="s">
         <v>723</v>
       </c>
-      <c r="D253" s="8" t="s">
-        <v>724</v>
-      </c>
       <c r="E253" s="17" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F253" s="4">
         <v>244987</v>
@@ -9074,19 +9075,19 @@
     </row>
     <row r="254" spans="1:6" ht="15" thickBot="1">
       <c r="A254" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B254" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="C254" s="8" t="s">
         <v>725</v>
       </c>
-      <c r="C254" s="8" t="s">
+      <c r="D254" s="8" t="s">
         <v>726</v>
       </c>
-      <c r="D254" s="8" t="s">
+      <c r="E254" s="17" t="s">
         <v>727</v>
-      </c>
-      <c r="E254" s="17" t="s">
-        <v>728</v>
       </c>
       <c r="F254" s="4">
         <v>241465</v>
@@ -9094,19 +9095,19 @@
     </row>
     <row r="255" spans="1:6" ht="15" thickBot="1">
       <c r="A255" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B255" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="C255" s="8" t="s">
         <v>729</v>
       </c>
-      <c r="C255" s="8" t="s">
+      <c r="D255" s="8" t="s">
         <v>730</v>
       </c>
-      <c r="D255" s="8" t="s">
+      <c r="E255" s="17" t="s">
         <v>731</v>
-      </c>
-      <c r="E255" s="17" t="s">
-        <v>732</v>
       </c>
       <c r="F255" s="31">
         <v>245352</v>
@@ -9114,19 +9115,19 @@
     </row>
     <row r="256" spans="1:6" ht="15" thickBot="1">
       <c r="A256" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B256" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="C256" s="8" t="s">
         <v>733</v>
       </c>
-      <c r="C256" s="8" t="s">
+      <c r="D256" s="8" t="s">
         <v>734</v>
       </c>
-      <c r="D256" s="8" t="s">
+      <c r="E256" s="17" t="s">
         <v>735</v>
-      </c>
-      <c r="E256" s="17" t="s">
-        <v>736</v>
       </c>
       <c r="F256" s="4">
         <v>244622</v>
@@ -9134,19 +9135,19 @@
     </row>
     <row r="257" spans="1:6" ht="15" thickBot="1">
       <c r="A257" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B257" s="3" t="s">
+        <v>736</v>
+      </c>
+      <c r="C257" s="8" t="s">
         <v>737</v>
       </c>
-      <c r="C257" s="8" t="s">
+      <c r="D257" s="8" t="s">
         <v>738</v>
       </c>
-      <c r="D257" s="8" t="s">
-        <v>739</v>
-      </c>
       <c r="E257" s="17" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="F257" s="4">
         <v>244622</v>
@@ -9154,19 +9155,19 @@
     </row>
     <row r="258" spans="1:6" ht="15" thickBot="1">
       <c r="A258" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C258" s="8" t="s">
+        <v>739</v>
+      </c>
+      <c r="D258" s="8" t="s">
         <v>740</v>
       </c>
-      <c r="D258" s="8" t="s">
-        <v>741</v>
-      </c>
       <c r="E258" s="17" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F258" s="4">
         <v>244987</v>
@@ -9174,19 +9175,19 @@
     </row>
     <row r="259" spans="1:6" ht="15" thickBot="1">
       <c r="A259" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C259" s="8" t="s">
+        <v>741</v>
+      </c>
+      <c r="D259" s="8" t="s">
         <v>742</v>
       </c>
-      <c r="D259" s="8" t="s">
+      <c r="E259" s="17" t="s">
         <v>743</v>
-      </c>
-      <c r="E259" s="17" t="s">
-        <v>744</v>
       </c>
       <c r="F259" s="4">
         <v>244622</v>
@@ -9194,19 +9195,19 @@
     </row>
     <row r="260" spans="1:6" ht="19" thickBot="1">
       <c r="A260" s="5" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B260" s="25" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C260" s="6">
         <v>3164</v>
       </c>
       <c r="D260" s="6" t="s">
+        <v>745</v>
+      </c>
+      <c r="E260" s="17" t="s">
         <v>746</v>
-      </c>
-      <c r="E260" s="17" t="s">
-        <v>747</v>
       </c>
       <c r="F260" s="31">
         <v>245352</v>
@@ -9214,19 +9215,19 @@
     </row>
     <row r="261" spans="1:6" ht="15" thickBot="1">
       <c r="A261" s="5" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C261" s="6">
         <v>3168</v>
       </c>
       <c r="D261" s="6" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E261" s="17" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="F261" s="31">
         <v>245352</v>
@@ -9234,19 +9235,19 @@
     </row>
     <row r="262" spans="1:6" ht="15" thickBot="1">
       <c r="A262" s="5" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B262" s="5" t="s">
+        <v>749</v>
+      </c>
+      <c r="C262" s="12" t="s">
         <v>750</v>
       </c>
-      <c r="C262" s="12" t="s">
+      <c r="D262" s="6" t="s">
         <v>751</v>
       </c>
-      <c r="D262" s="6" t="s">
+      <c r="E262" s="17" t="s">
         <v>752</v>
-      </c>
-      <c r="E262" s="17" t="s">
-        <v>753</v>
       </c>
       <c r="F262" s="4">
         <v>244622</v>
@@ -9254,19 +9255,19 @@
     </row>
     <row r="263" spans="1:6" ht="15" thickBot="1">
       <c r="A263" s="5" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B263" s="5" t="s">
+        <v>753</v>
+      </c>
+      <c r="C263" s="12" t="s">
         <v>754</v>
       </c>
-      <c r="C263" s="12" t="s">
+      <c r="D263" s="6" t="s">
         <v>755</v>
       </c>
-      <c r="D263" s="6" t="s">
-        <v>756</v>
-      </c>
       <c r="E263" s="17" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F263" s="4">
         <v>244987</v>
@@ -9274,19 +9275,19 @@
     </row>
     <row r="264" spans="1:6" ht="15" thickBot="1">
       <c r="A264" s="25" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B264" s="25" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C264" s="32">
         <v>3165</v>
       </c>
       <c r="D264" s="6" t="s">
+        <v>757</v>
+      </c>
+      <c r="E264" s="17" t="s">
         <v>758</v>
-      </c>
-      <c r="E264" s="17" t="s">
-        <v>759</v>
       </c>
       <c r="F264" s="31">
         <v>242430</v>
@@ -9294,19 +9295,19 @@
     </row>
     <row r="265" spans="1:6" ht="15" thickBot="1">
       <c r="A265" s="25" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B265" s="25" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C265" s="6">
         <v>3166</v>
       </c>
       <c r="D265" s="6" t="s">
+        <v>759</v>
+      </c>
+      <c r="E265" s="17" t="s">
         <v>760</v>
-      </c>
-      <c r="E265" s="17" t="s">
-        <v>761</v>
       </c>
       <c r="F265" s="31">
         <v>242430</v>
@@ -9314,19 +9315,19 @@
     </row>
     <row r="266" spans="1:6" ht="15" thickBot="1">
       <c r="A266" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B266" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="C266" s="3" t="s">
         <v>762</v>
       </c>
-      <c r="C266" s="3" t="s">
+      <c r="D266" s="3" t="s">
         <v>763</v>
       </c>
-      <c r="D266" s="3" t="s">
+      <c r="E266" s="16" t="s">
         <v>764</v>
-      </c>
-      <c r="E266" s="16" t="s">
-        <v>765</v>
       </c>
       <c r="F266" s="4">
         <v>244622</v>
@@ -9334,19 +9335,19 @@
     </row>
     <row r="267" spans="1:6" ht="15" thickBot="1">
       <c r="A267" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C267" s="3" t="s">
+        <v>765</v>
+      </c>
+      <c r="D267" s="3" t="s">
         <v>766</v>
       </c>
-      <c r="D267" s="3" t="s">
-        <v>767</v>
-      </c>
       <c r="E267" s="16" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="F267" s="4">
         <v>244622</v>
@@ -9354,99 +9355,99 @@
     </row>
     <row r="268" spans="1:6" ht="15" thickBot="1">
       <c r="A268" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C268" s="3" t="s">
-        <v>768</v>
+        <v>843</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>769</v>
+        <v>844</v>
       </c>
       <c r="E268" s="16" t="s">
-        <v>714</v>
+        <v>764</v>
       </c>
       <c r="F268" s="4">
-        <v>244987</v>
+        <v>244622</v>
       </c>
     </row>
     <row r="269" spans="1:6" ht="15" thickBot="1">
       <c r="A269" s="3" t="s">
-        <v>710</v>
-      </c>
-      <c r="B269" s="33" t="s">
-        <v>770</v>
-      </c>
-      <c r="C269" s="33" t="s">
-        <v>771</v>
-      </c>
-      <c r="D269" s="33" t="s">
-        <v>772</v>
+        <v>709</v>
+      </c>
+      <c r="B269" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="C269" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="D269" s="3" t="s">
+        <v>768</v>
       </c>
       <c r="E269" s="16" t="s">
-        <v>773</v>
-      </c>
-      <c r="F269" s="31">
-        <v>245352</v>
+        <v>713</v>
+      </c>
+      <c r="F269" s="4">
+        <v>244987</v>
       </c>
     </row>
     <row r="270" spans="1:6" ht="15" thickBot="1">
       <c r="A270" s="3" t="s">
-        <v>710</v>
-      </c>
-      <c r="B270" s="3" t="s">
-        <v>774</v>
-      </c>
-      <c r="C270" s="3" t="s">
-        <v>775</v>
-      </c>
-      <c r="D270" s="10" t="s">
-        <v>776</v>
+        <v>709</v>
+      </c>
+      <c r="B270" s="33" t="s">
+        <v>769</v>
+      </c>
+      <c r="C270" s="33" t="s">
+        <v>770</v>
+      </c>
+      <c r="D270" s="33" t="s">
+        <v>771</v>
       </c>
       <c r="E270" s="16" t="s">
-        <v>714</v>
-      </c>
-      <c r="F270" s="4">
-        <v>244987</v>
+        <v>772</v>
+      </c>
+      <c r="F270" s="31">
+        <v>245352</v>
       </c>
     </row>
     <row r="271" spans="1:6" ht="15" thickBot="1">
       <c r="A271" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>778</v>
-      </c>
-      <c r="D271" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="E271" s="17" t="s">
-        <v>718</v>
+        <v>774</v>
+      </c>
+      <c r="D271" s="10" t="s">
+        <v>775</v>
+      </c>
+      <c r="E271" s="16" t="s">
+        <v>713</v>
       </c>
       <c r="F271" s="4">
-        <v>244622</v>
+        <v>244987</v>
       </c>
     </row>
     <row r="272" spans="1:6" ht="15" thickBot="1">
       <c r="A272" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="C272" s="3" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="D272" s="3" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="E272" s="17" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="F272" s="4">
         <v>244622</v>
@@ -9454,36 +9455,36 @@
     </row>
     <row r="273" spans="1:6" ht="15" thickBot="1">
       <c r="A273" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="C273" s="3" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>785</v>
-      </c>
-      <c r="E273" s="16" t="s">
-        <v>358</v>
+        <v>781</v>
+      </c>
+      <c r="E273" s="17" t="s">
+        <v>717</v>
       </c>
       <c r="F273" s="4">
-        <v>244987</v>
+        <v>244622</v>
       </c>
     </row>
     <row r="274" spans="1:6" ht="15" thickBot="1">
       <c r="A274" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="C274" s="3" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="D274" s="3" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="E274" s="16" t="s">
         <v>358</v>
@@ -9494,39 +9495,39 @@
     </row>
     <row r="275" spans="1:6" ht="15" thickBot="1">
       <c r="A275" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B275" s="3" t="s">
+        <v>785</v>
+      </c>
+      <c r="C275" s="3" t="s">
         <v>786</v>
       </c>
-      <c r="C275" s="3" t="s">
-        <v>789</v>
-      </c>
       <c r="D275" s="3" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="E275" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="F275" s="31">
-        <v>245352</v>
+        <v>358</v>
+      </c>
+      <c r="F275" s="4">
+        <v>244987</v>
       </c>
     </row>
     <row r="276" spans="1:6" ht="15" thickBot="1">
       <c r="A276" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="C276" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="D276" s="10" t="s">
-        <v>793</v>
+        <v>788</v>
+      </c>
+      <c r="D276" s="3" t="s">
+        <v>789</v>
       </c>
       <c r="E276" s="16" t="s">
-        <v>747</v>
+        <v>731</v>
       </c>
       <c r="F276" s="31">
         <v>245352</v>
@@ -9534,39 +9535,39 @@
     </row>
     <row r="277" spans="1:6" ht="15" thickBot="1">
       <c r="A277" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="C277" s="3" t="s">
-        <v>795</v>
-      </c>
-      <c r="D277" s="3" t="s">
-        <v>796</v>
-      </c>
-      <c r="E277" s="17" t="s">
-        <v>718</v>
-      </c>
-      <c r="F277" s="4">
-        <v>244622</v>
+        <v>791</v>
+      </c>
+      <c r="D277" s="10" t="s">
+        <v>792</v>
+      </c>
+      <c r="E277" s="16" t="s">
+        <v>746</v>
+      </c>
+      <c r="F277" s="31">
+        <v>245352</v>
       </c>
     </row>
     <row r="278" spans="1:6" ht="15" thickBot="1">
       <c r="A278" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B278" s="3" t="s">
+        <v>793</v>
+      </c>
+      <c r="C278" s="3" t="s">
         <v>794</v>
       </c>
-      <c r="C278" s="3" t="s">
-        <v>797</v>
-      </c>
       <c r="D278" s="3" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="E278" s="17" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="F278" s="4">
         <v>244622</v>
@@ -9574,39 +9575,39 @@
     </row>
     <row r="279" spans="1:6" ht="15" thickBot="1">
       <c r="A279" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
       <c r="C279" s="3" t="s">
-        <v>800</v>
-      </c>
-      <c r="D279" s="10" t="s">
-        <v>801</v>
-      </c>
-      <c r="E279" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="F279" s="31">
-        <v>245352</v>
+        <v>796</v>
+      </c>
+      <c r="D279" s="3" t="s">
+        <v>797</v>
+      </c>
+      <c r="E279" s="17" t="s">
+        <v>717</v>
+      </c>
+      <c r="F279" s="4">
+        <v>244622</v>
       </c>
     </row>
     <row r="280" spans="1:6" ht="15" thickBot="1">
       <c r="A280" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>803</v>
-      </c>
-      <c r="D280" s="3" t="s">
-        <v>804</v>
+        <v>799</v>
+      </c>
+      <c r="D280" s="10" t="s">
+        <v>800</v>
       </c>
       <c r="E280" s="16" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="F280" s="31">
         <v>245352</v>
@@ -9614,19 +9615,19 @@
     </row>
     <row r="281" spans="1:6" ht="15" thickBot="1">
       <c r="A281" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B281" s="3" t="s">
+        <v>801</v>
+      </c>
+      <c r="C281" s="3" t="s">
         <v>802</v>
       </c>
-      <c r="C281" s="3" t="s">
-        <v>805</v>
-      </c>
       <c r="D281" s="3" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="E281" s="16" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="F281" s="31">
         <v>245352</v>
@@ -9634,19 +9635,19 @@
     </row>
     <row r="282" spans="1:6" ht="15" thickBot="1">
       <c r="A282" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="E282" s="16" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="F282" s="31">
         <v>245352</v>
@@ -9654,39 +9655,39 @@
     </row>
     <row r="283" spans="1:6" ht="15" thickBot="1">
       <c r="A283" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="C283" s="3" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>812</v>
-      </c>
-      <c r="E283" s="17" t="s">
-        <v>718</v>
-      </c>
-      <c r="F283" s="4">
-        <v>244622</v>
+        <v>808</v>
+      </c>
+      <c r="E283" s="16" t="s">
+        <v>731</v>
+      </c>
+      <c r="F283" s="31">
+        <v>245352</v>
       </c>
     </row>
     <row r="284" spans="1:6" ht="15" thickBot="1">
       <c r="A284" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="E284" s="17" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="F284" s="4">
         <v>244622</v>
@@ -9694,128 +9695,132 @@
     </row>
     <row r="285" spans="1:6" ht="15" thickBot="1">
       <c r="A285" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>818</v>
-      </c>
-      <c r="E285" s="16" t="s">
-        <v>714</v>
+        <v>814</v>
+      </c>
+      <c r="E285" s="17" t="s">
+        <v>717</v>
       </c>
       <c r="F285" s="4">
-        <v>244987</v>
+        <v>244622</v>
       </c>
     </row>
     <row r="286" spans="1:6" ht="15" thickBot="1">
       <c r="A286" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B286" s="3" t="s">
+        <v>815</v>
+      </c>
+      <c r="C286" s="3" t="s">
         <v>816</v>
       </c>
-      <c r="C286" s="3" t="s">
-        <v>819</v>
-      </c>
       <c r="D286" s="3" t="s">
-        <v>820</v>
-      </c>
-      <c r="E286" s="17" t="s">
-        <v>718</v>
+        <v>817</v>
+      </c>
+      <c r="E286" s="16" t="s">
+        <v>713</v>
       </c>
       <c r="F286" s="4">
-        <v>244622</v>
+        <v>244987</v>
       </c>
     </row>
     <row r="287" spans="1:6" ht="15" thickBot="1">
       <c r="A287" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B287" s="3" t="s">
+        <v>815</v>
+      </c>
+      <c r="C287" s="3" t="s">
+        <v>818</v>
+      </c>
+      <c r="D287" s="3" t="s">
+        <v>819</v>
+      </c>
+      <c r="E287" s="17" t="s">
+        <v>717</v>
+      </c>
+      <c r="F287" s="4">
+        <v>244622</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" ht="15" thickBot="1">
+      <c r="A288" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="B288" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="C288" s="3" t="s">
         <v>821</v>
       </c>
-      <c r="C287" s="3" t="s">
+      <c r="D288" s="3" t="s">
         <v>822</v>
       </c>
-      <c r="D287" s="3" t="s">
+      <c r="E288" s="16" t="s">
+        <v>713</v>
+      </c>
+      <c r="F288" s="4">
+        <v>244987</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" ht="15" thickBot="1">
+      <c r="A289" s="5" t="s">
+        <v>709</v>
+      </c>
+      <c r="B289" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="C289" s="6" t="s">
         <v>823</v>
       </c>
-      <c r="E287" s="16" t="s">
-        <v>714</v>
-      </c>
-      <c r="F287" s="4">
-        <v>244987</v>
-      </c>
-    </row>
-    <row r="288" spans="1:6" ht="15" thickBot="1">
-      <c r="A288" s="5" t="s">
-        <v>710</v>
-      </c>
-      <c r="B288" s="5" t="s">
-        <v>770</v>
-      </c>
-      <c r="C288" s="6" t="s">
+      <c r="D289" s="6" t="s">
         <v>824</v>
       </c>
-      <c r="D288" s="6" t="s">
-        <v>825</v>
-      </c>
-      <c r="E288" s="6"/>
-      <c r="F288" s="6"/>
-    </row>
-    <row r="289" spans="1:6" ht="15" thickBot="1">
-      <c r="A289" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="B289" s="6" t="s">
-        <v>826</v>
-      </c>
-      <c r="C289" s="6" t="s">
-        <v>827</v>
-      </c>
-      <c r="D289" s="6" t="s">
-        <v>828</v>
-      </c>
-      <c r="E289" s="6" t="s">
-        <v>829</v>
-      </c>
-      <c r="F289" s="4">
-        <v>245413</v>
-      </c>
+      <c r="E289" s="6"/>
+      <c r="F289" s="6"/>
     </row>
     <row r="290" spans="1:6" ht="15" thickBot="1">
       <c r="A290" s="6" t="s">
-        <v>402</v>
+        <v>84</v>
       </c>
       <c r="B290" s="6" t="s">
-        <v>571</v>
+        <v>825</v>
       </c>
       <c r="C290" s="6" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="D290" s="6" t="s">
-        <v>831</v>
-      </c>
-      <c r="E290" s="6"/>
-      <c r="F290" s="6"/>
+        <v>827</v>
+      </c>
+      <c r="E290" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="F290" s="4">
+        <v>245413</v>
+      </c>
     </row>
     <row r="291" spans="1:6" ht="15" thickBot="1">
       <c r="A291" s="6" t="s">
         <v>402</v>
       </c>
       <c r="B291" s="6" t="s">
-        <v>436</v>
+        <v>571</v>
       </c>
       <c r="C291" s="6" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="D291" s="6" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="E291" s="6"/>
       <c r="F291" s="6"/>
@@ -9825,19 +9830,35 @@
         <v>402</v>
       </c>
       <c r="B292" s="6" t="s">
-        <v>621</v>
+        <v>436</v>
       </c>
       <c r="C292" s="6" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="D292" s="6" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="E292" s="6"/>
       <c r="F292" s="6"/>
     </row>
+    <row r="293" spans="1:6" ht="15" thickBot="1">
+      <c r="A293" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="B293" s="6" t="s">
+        <v>620</v>
+      </c>
+      <c r="C293" s="6" t="s">
+        <v>833</v>
+      </c>
+      <c r="D293" s="6" t="s">
+        <v>834</v>
+      </c>
+      <c r="E293" s="6"/>
+      <c r="F293" s="6"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:F292" xr:uid="{F0F44DC9-5D0B-4F37-AFB6-F7D483AECB79}"/>
+  <autoFilter ref="A2:F293" xr:uid="{F0F44DC9-5D0B-4F37-AFB6-F7D483AECB79}"/>
   <mergeCells count="1">
     <mergeCell ref="E1:F1"/>
   </mergeCells>
